--- a/one down/普物實驗/13 普朗克常數的測定/E24146107_王翊權_預報13_表格.xlsx
+++ b/one down/普物實驗/13 普朗克常數的測定/E24146107_王翊權_預報13_表格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Wang\.gemini\Workspaces\school\one down\普物實驗\13 普朗克常數的測定\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\13 普朗克常數的測定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5EFB10-DC15-4CD8-AFD2-7833BF3CF3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC754766-EE66-4600-8EB0-EE8E6F11AC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -47,152 +47,10 @@
     <t>L(m)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="DFKai-SB"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>1/L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>(m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="DFKai-SB"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>I(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>μ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>A)</t>
-    </r>
-  </si>
-  <si>
     <t>B：測量水銀燈五條主要譜線的截流電壓</t>
   </si>
   <si>
     <t>譜線</t>
-  </si>
-  <si>
-    <t>頻率
-(Hz)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="DFKai-SB"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>最大電流
-I</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>μ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="標楷體"/>
-        <family val="4"/>
-        <charset val="136"/>
-      </rPr>
-      <t>A)</t>
-    </r>
-  </si>
-  <si>
-    <t>載流電壓
-V(V)</t>
   </si>
   <si>
     <t>紫外</t>
@@ -227,17 +85,123 @@
   <si>
     <t>功函數</t>
   </si>
+  <si>
+    <t>截流電壓
+V(V)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>頻率
+(Hz)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1/L</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="DFKai-SB"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="DFKai-SB"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>(m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="DFKai-SB"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="DFKai-SB"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>μ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>A)</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>最大電流
+I</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>(μA)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
     <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -256,18 +220,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="DFKai-SB"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
     </font>
@@ -303,6 +255,34 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="DFKai-SB"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -318,7 +298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -618,32 +598,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
@@ -747,11 +701,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -794,96 +762,106 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -896,6 +874,2195 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$E$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>截流電壓
+V(V)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-TW"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>工作表1!$C$38:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>822000000000000.13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>741000000000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>688000000000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>549000000000000</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.00E+00">
+                  <c:v>520000000000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>工作表1!$E$38:$E$43</c:f>
+              <c:numCache>
+                <c:formatCode>0.000_ </c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>1.3540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2070000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.036</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.629</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.4047</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2C27-4007-80CA-E5B90BC853F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="72052416"/>
+        <c:axId val="72051936"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="72052416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="500000000000000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US"/>
+                  <a:t>頻率</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>(Hz)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="72051936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="72051936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US"/>
+                  <a:t>截流電壓</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>V</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="72052416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>I(μA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>工作表1!$D$4:$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.717421124828531</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.890606420927464</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.405827263267426</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.1827364554637239</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1632653061224438</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.3046018991964896</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5746219592373398</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9488399762046358</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.4083288263926406</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.9382716049382678</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.5269352648257097</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1649312786338992</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.8446751249519382</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>工作表1!$E$4:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000_ </c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.6279999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.375</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2589999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1628000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0613999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98380000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.90580000000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8337</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.77980000000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.62580000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.57669999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3400-41A4-A6E9-644B3741A70F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="154427488"/>
+        <c:axId val="154428448"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="154427488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>1/L2(m-2)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154428448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="154428448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>I(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" altLang="zh-TW"/>
+                  <a:t>μ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>A)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154427488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>235857</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>41675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>494127</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>95463</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D436A93-25C2-B779-6294-531F3721779A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>493059</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>214032</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>134471</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43702</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E48D5B-C7D7-3DE2-C86D-69D073FFF580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1099,7 +3266,11 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="8.09765625" customWidth="1"/>
+    <col min="1" max="2" width="8.09765625" customWidth="1"/>
+    <col min="3" max="3" width="20.69921875" customWidth="1"/>
+    <col min="4" max="5" width="8.09765625" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="26" width="8.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
@@ -1169,10 +3340,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1208,7 +3379,9 @@
         <f t="shared" ref="D4:D17" si="0">1/C4^2</f>
         <v>16</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="9">
+        <v>1.6279999999999999</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1244,7 +3417,9 @@
         <f t="shared" si="0"/>
         <v>13.717421124828531</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="9">
+        <v>1.48</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1280,7 +3455,9 @@
         <f t="shared" si="0"/>
         <v>11.890606420927464</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9">
+        <v>1.375</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1316,7 +3493,9 @@
         <f t="shared" si="0"/>
         <v>10.405827263267426</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="9">
+        <v>1.2589999999999999</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1352,7 +3531,9 @@
         <f t="shared" si="0"/>
         <v>9.1827364554637239</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="9">
+        <v>1.1628000000000001</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1388,7 +3569,9 @@
         <f t="shared" si="0"/>
         <v>8.1632653061224438</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="9">
+        <v>1.0613999999999999</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1424,7 +3607,9 @@
         <f t="shared" si="0"/>
         <v>7.3046018991964896</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="9">
+        <v>0.98380000000000001</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1460,7 +3645,9 @@
         <f t="shared" si="0"/>
         <v>6.5746219592373398</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="9">
+        <v>0.90580000000000005</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1496,7 +3683,9 @@
         <f t="shared" si="0"/>
         <v>5.9488399762046358</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="9">
+        <v>0.8337</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1532,7 +3721,9 @@
         <f t="shared" si="0"/>
         <v>5.4083288263926406</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9">
+        <v>0.77980000000000005</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1568,7 +3759,9 @@
         <f t="shared" si="0"/>
         <v>4.9382716049382678</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="9">
+        <v>0.72</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1604,7 +3797,9 @@
         <f t="shared" si="0"/>
         <v>4.5269352648257097</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="9">
+        <v>0.66739999999999999</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1640,7 +3835,9 @@
         <f t="shared" si="0"/>
         <v>4.1649312786338992</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="9">
+        <v>0.62580000000000002</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1676,7 +3873,9 @@
         <f t="shared" si="0"/>
         <v>3.8446751249519382</v>
       </c>
-      <c r="E17" s="13"/>
+      <c r="E17" s="13">
+        <v>0.57669999999999999</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1757,13 +3956,6 @@
     </row>
     <row r="20" spans="1:26" ht="18" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1787,19 +3979,6 @@
     </row>
     <row r="21" spans="1:26" ht="29.4" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1823,11 +4002,6 @@
     </row>
     <row r="22" spans="1:26" ht="27" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -1851,16 +4025,6 @@
     </row>
     <row r="23" spans="1:26" ht="18" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <f>8.22*10^14</f>
-        <v>822000000000000.13</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1884,16 +4048,6 @@
     </row>
     <row r="24" spans="1:26" ht="18" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <f>7.41*10^14</f>
-        <v>741000000000000</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1902,7 +4056,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="17"/>
+      <c r="O24" s="14"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -1917,16 +4071,6 @@
     </row>
     <row r="25" spans="1:26" ht="18" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="7">
-        <f>6.88*10^14</f>
-        <v>688000000000000</v>
-      </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1950,16 +4094,6 @@
     </row>
     <row r="26" spans="1:26" ht="18" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="7">
-        <f>5.49*10^14</f>
-        <v>549000000000000</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1983,18 +4117,6 @@
     </row>
     <row r="27" spans="1:26" ht="18" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="19">
-        <f>5.2*10^14</f>
-        <v>520000000000000</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -2018,16 +4140,6 @@
     </row>
     <row r="28" spans="1:26" ht="18" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="17">
-        <f>D29 / 1.6 / 10^-19</f>
-        <v>4.1437500000000003E-15</v>
-      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2051,16 +4163,6 @@
     </row>
     <row r="29" spans="1:26" ht="18" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="42">
-        <f>6.63*10^-34</f>
-        <v>6.6300000000000008E-34</v>
-      </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -2084,16 +4186,6 @@
     </row>
     <row r="30" spans="1:26" ht="18" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="28">
-        <f>D28 * 1.6 * 10^-19</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2117,16 +4209,6 @@
     </row>
     <row r="31" spans="1:26" ht="18" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="30">
-        <f>ABS((D29-D30)/D29*100)</f>
-        <v>100</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2150,11 +4232,6 @@
     </row>
     <row r="32" spans="1:26" ht="18" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2178,15 +4255,6 @@
     </row>
     <row r="33" spans="1:26" ht="18" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2210,16 +4278,6 @@
     </row>
     <row r="34" spans="1:26" ht="18" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="22">
-        <f>(D29*C23-1.6*10^-19*E23)/1.6/10^-19</f>
-        <v>3.4061625000000011</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2243,16 +4301,6 @@
     </row>
     <row r="35" spans="1:26" ht="18" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="22">
-        <f>(D29*C24-1.6*10^-19*E24)/1.6/10^-19</f>
-        <v>3.0705187500000006</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2274,18 +4322,15 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="18" customHeight="1">
+    <row r="36" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="6" t="s">
-        <v>12</v>
+      <c r="B36" s="15" t="s">
+        <v>3</v>
       </c>
-      <c r="C36" s="22">
-        <f>(D29*C25-1.6*10^-19*E25)/1.6/10^-19</f>
-        <v>2.8509000000000002</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2307,18 +4352,21 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="18" customHeight="1">
+    <row r="37" spans="1:26" ht="18" customHeight="1" thickTop="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="6" t="s">
-        <v>13</v>
+      <c r="B37" s="38" t="s">
+        <v>4</v>
       </c>
-      <c r="C37" s="22">
-        <f>(D29*C26-1.6*10^-19*E26)/1.6/10^-19</f>
-        <v>2.2749187500000003</v>
+      <c r="C37" s="40" t="s">
+        <v>17</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="D37" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="16"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2342,16 +4390,11 @@
     </row>
     <row r="38" spans="1:26" ht="18" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="23">
-        <f>(D29*C27-1.6*10^-19*E27)/1.6/10^-19</f>
-        <v>2.1547500000000004</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="16"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2375,11 +4418,20 @@
     </row>
     <row r="39" spans="1:26" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="B39" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="18">
+        <f>8.22*10^14</f>
+        <v>822000000000000.13</v>
+      </c>
+      <c r="D39" s="19">
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="E39" s="20">
+        <v>1.3540000000000001</v>
+      </c>
+      <c r="F39" s="16"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2403,11 +4455,20 @@
     </row>
     <row r="40" spans="1:26" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="B40" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="18">
+        <f>7.41*10^14</f>
+        <v>741000000000000</v>
+      </c>
+      <c r="D40" s="19">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="E40" s="20">
+        <v>1.2070000000000001</v>
+      </c>
+      <c r="F40" s="16"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2431,11 +4492,20 @@
     </row>
     <row r="41" spans="1:26" ht="18" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="B41" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="18">
+        <f>6.88*10^14</f>
+        <v>688000000000000</v>
+      </c>
+      <c r="D41" s="19">
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="E41" s="20">
+        <v>1.036</v>
+      </c>
+      <c r="F41" s="16"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2459,11 +4529,20 @@
     </row>
     <row r="42" spans="1:26" ht="18" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="B42" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="18">
+        <f>5.49*10^14</f>
+        <v>549000000000000</v>
+      </c>
+      <c r="D42" s="19">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="E42" s="20">
+        <v>0.629</v>
+      </c>
+      <c r="F42" s="16"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -2485,13 +4564,24 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="18" customHeight="1">
+    <row r="43" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="B43" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="22">
+        <f>5.2*10^14</f>
+        <v>520000000000000</v>
+      </c>
+      <c r="D43" s="23">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="E43" s="24">
+        <v>0.4047</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>10</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2513,13 +4603,21 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="18" customHeight="1">
+    <row r="44" spans="1:26" ht="18" customHeight="1" thickTop="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
+      <c r="B44" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="45"/>
+      <c r="D44" s="36">
+        <f>3*10^-15</f>
+        <v>3.0000000000000002E-15</v>
+      </c>
+      <c r="E44" s="33"/>
+      <c r="F44" s="25">
+        <f>D45/1.6/10^-19</f>
+        <v>4.1437500000000003E-15</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -2543,11 +4641,16 @@
     </row>
     <row r="45" spans="1:26" ht="18" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="B45" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="29"/>
+      <c r="D45" s="36">
+        <f>6.63*10^-34</f>
+        <v>6.6300000000000008E-34</v>
+      </c>
+      <c r="E45" s="37"/>
+      <c r="F45" s="16"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -2571,11 +4674,16 @@
     </row>
     <row r="46" spans="1:26" ht="18" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="B46" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="29"/>
+      <c r="D46" s="32">
+        <f>D44* 1.6 * 10^-19</f>
+        <v>4.8000000000000007E-34</v>
+      </c>
+      <c r="E46" s="33"/>
+      <c r="F46" s="16"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2597,13 +4705,18 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="18" customHeight="1">
+    <row r="47" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+      <c r="B47" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="31"/>
+      <c r="D47" s="34">
+        <f>ABS((D45-D46)/D45)</f>
+        <v>0.27601809954751128</v>
+      </c>
+      <c r="E47" s="35"/>
+      <c r="F47" s="16"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2625,7 +4738,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="18" customHeight="1">
+    <row r="48" spans="1:26" ht="18" customHeight="1" thickTop="1" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2653,10 +4766,14 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="18" customHeight="1">
+    <row r="49" spans="1:26" ht="18" customHeight="1" thickTop="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
+      <c r="B49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2683,8 +4800,13 @@
     </row>
     <row r="50" spans="1:26" ht="18" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
+      <c r="B50" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="26">
+        <f>(D44*C39-1.6*10^-19*E39)/1.6/10^-19</f>
+        <v>1.5412500000000002E+19</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2711,8 +4833,13 @@
     </row>
     <row r="51" spans="1:26" ht="18" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="26">
+        <f>(D44*C40-1.6*10^-19*E40)/1.6/10^-19</f>
+        <v>1.389375E+19</v>
+      </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2739,8 +4866,13 @@
     </row>
     <row r="52" spans="1:26" ht="18" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+      <c r="B52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="26">
+        <f>(D44*C41-1.6*10^-19*E41)/1.6/10^-19</f>
+        <v>1.29E+19</v>
+      </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2767,8 +4899,13 @@
     </row>
     <row r="53" spans="1:26" ht="18" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="B53" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="26">
+        <f>(D44*C42-1.6*10^-19*E42)/1.6/10^-19</f>
+        <v>1.029375E+19</v>
+      </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -2793,10 +4930,15 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="18" customHeight="1">
+    <row r="54" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
+      <c r="B54" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="27">
+        <f>(D44*C43-1.6*10^-19*E43)/1.6/10^-19</f>
+        <v>9.75E+18</v>
+      </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -2821,7 +4963,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="18" customHeight="1">
+    <row r="55" spans="1:26" ht="18" customHeight="1" thickTop="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -29311,21 +31453,22 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/one down/普物實驗/13 普朗克常數的測定/E24146107_王翊權_預報13_表格.xlsx
+++ b/one down/普物實驗/13 普朗克常數的測定/E24146107_王翊權_預報13_表格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\13 普朗克常數的測定\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Wang\.gemini\Workspaces\school\one down\普物實驗\13 普朗克常數的測定\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC754766-EE66-4600-8EB0-EE8E6F11AC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E32FC5-C909-4932-8DE9-122B09BEEE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>A：驗證照度與距離平方成反比</t>
   </si>
@@ -152,6 +152,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>μ</t>
     </r>
@@ -160,6 +161,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>A)</t>
     </r>
@@ -234,11 +236,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
@@ -259,6 +263,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -308,21 +313,6 @@
     </border>
     <border>
       <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -415,7 +405,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="thick">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -430,181 +420,10 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -637,8 +456,340 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thick">
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -650,28 +801,32 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -679,36 +834,29 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -719,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -738,28 +886,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -774,40 +901,82 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -816,47 +985,44 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1469,10 +1635,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>工作表1!$D$4:$D$17</c:f>
+              <c:f>工作表1!$D$4:$D$22</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>16</c:v>
                 </c:pt>
@@ -1515,15 +1681,30 @@
                 <c:pt idx="13">
                   <c:v>3.8446751249519382</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.5599857600569567</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3057851239669391</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.0778701138811915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.8727377190462482</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.687449610319804</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>工作表1!$E$4:$E$17</c:f>
+              <c:f>工作表1!$E$4:$E$22</c:f>
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1.6279999999999999</c:v>
                 </c:pt>
@@ -1566,6 +1747,21 @@
                 <c:pt idx="13">
                   <c:v>0.57669999999999999</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.54200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.49890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.46879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.4325</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.41489999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1573,6 +1769,533 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-3400-41A4-A6E9-644B3741A70F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="154427488"/>
+        <c:axId val="154428448"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="154427488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>1/L2(m-2)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154428448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="154428448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>I(</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" altLang="zh-TW"/>
+                  <a:t>μ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>A)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154427488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>I(μA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>工作表1!$I$4:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.717421124828531</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.890606420927464</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.405827263267426</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.1827364554637239</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.1632653061224438</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.3046018991964896</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5746219592373398</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.9488399762046358</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.4083288263926406</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.9382716049382678</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.5269352648257097</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1649312786338992</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.8446751249519382</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.5599857600569567</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3057851239669391</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.0778701138811915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.8727377190462482</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.687449610319804</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>工作表1!$J$4:$J$22</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2.67</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.41</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-33BB-418D-A30D-3B39EA4C1423}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1917,6 +2640,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2988,20 +3751,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>235857</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>41675</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>205377</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>3575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>494127</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>95463</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>463647</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>57363</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3028,16 +4307,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>493059</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>214032</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>218739</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114972</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>134471</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>43702</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>751691</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>173242</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3057,6 +4336,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>88750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{189A2859-DD04-4F61-81CA-F6F3C0BD1D96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3301,7 +4618,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
+    <row r="2" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -3333,23 +4650,31 @@
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="G3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -3369,24 +4694,33 @@
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="6">
+      <c r="B4" s="24">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="19">
         <v>0.25</v>
       </c>
-      <c r="D4" s="8">
-        <f t="shared" ref="D4:D17" si="0">1/C4^2</f>
+      <c r="D4" s="20">
+        <f t="shared" ref="D4:D22" si="0">1/C4^2</f>
         <v>16</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="25">
         <v>1.6279999999999999</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="G4" s="24">
+        <v>1</v>
+      </c>
+      <c r="H4" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="I4" s="20">
+        <f t="shared" ref="I4:I22" si="1">1/H4^2</f>
+        <v>16</v>
+      </c>
+      <c r="J4" s="25">
+        <v>2.67</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -3406,25 +4740,35 @@
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="6">
+      <c r="B5" s="24">
         <v>2</v>
       </c>
-      <c r="C5" s="7">
-        <f t="shared" ref="C5:C17" si="1">C4 + 0.02</f>
+      <c r="C5" s="19">
+        <f t="shared" ref="C5:C22" si="2">C4 + 0.02</f>
         <v>0.27</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="20">
         <f t="shared" si="0"/>
         <v>13.717421124828531</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="25">
         <v>1.48</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="G5" s="24">
+        <v>2</v>
+      </c>
+      <c r="H5" s="19">
+        <f t="shared" ref="H5:H22" si="3">H4 + 0.02</f>
+        <v>0.27</v>
+      </c>
+      <c r="I5" s="20">
+        <f t="shared" si="1"/>
+        <v>13.717421124828531</v>
+      </c>
+      <c r="J5" s="25">
+        <v>2.31</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3444,25 +4788,35 @@
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="6">
+      <c r="B6" s="24">
         <v>3</v>
       </c>
-      <c r="C6" s="7">
-        <f t="shared" si="1"/>
+      <c r="C6" s="19">
+        <f t="shared" si="2"/>
         <v>0.29000000000000004</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>11.890606420927464</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="25">
         <v>1.375</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="G6" s="24">
+        <v>3</v>
+      </c>
+      <c r="H6" s="19">
+        <f t="shared" si="3"/>
+        <v>0.29000000000000004</v>
+      </c>
+      <c r="I6" s="20">
+        <f t="shared" si="1"/>
+        <v>11.890606420927464</v>
+      </c>
+      <c r="J6" s="25">
+        <v>2.0099999999999998</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -3482,25 +4836,35 @@
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="6">
+      <c r="B7" s="24">
         <v>4</v>
       </c>
-      <c r="C7" s="7">
-        <f t="shared" si="1"/>
+      <c r="C7" s="19">
+        <f t="shared" si="2"/>
         <v>0.31000000000000005</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>10.405827263267426</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="25">
         <v>1.2589999999999999</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="G7" s="24">
+        <v>4</v>
+      </c>
+      <c r="H7" s="19">
+        <f t="shared" si="3"/>
+        <v>0.31000000000000005</v>
+      </c>
+      <c r="I7" s="20">
+        <f t="shared" si="1"/>
+        <v>10.405827263267426</v>
+      </c>
+      <c r="J7" s="25">
+        <v>1.78</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -3520,25 +4884,35 @@
     </row>
     <row r="8" spans="1:26" ht="18" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="6">
+      <c r="B8" s="24">
         <v>5</v>
       </c>
-      <c r="C8" s="7">
-        <f t="shared" si="1"/>
+      <c r="C8" s="19">
+        <f t="shared" si="2"/>
         <v>0.33000000000000007</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>9.1827364554637239</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="25">
         <v>1.1628000000000001</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="G8" s="24">
+        <v>5</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="3"/>
+        <v>0.33000000000000007</v>
+      </c>
+      <c r="I8" s="20">
+        <f t="shared" si="1"/>
+        <v>9.1827364554637239</v>
+      </c>
+      <c r="J8" s="25">
+        <v>1.57</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -3558,25 +4932,35 @@
     </row>
     <row r="9" spans="1:26" ht="18" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="6">
+      <c r="B9" s="24">
         <v>6</v>
       </c>
-      <c r="C9" s="7">
-        <f t="shared" si="1"/>
+      <c r="C9" s="19">
+        <f t="shared" si="2"/>
         <v>0.35000000000000009</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="20">
         <f t="shared" si="0"/>
         <v>8.1632653061224438</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="25">
         <v>1.0613999999999999</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="G9" s="24">
+        <v>6</v>
+      </c>
+      <c r="H9" s="19">
+        <f t="shared" si="3"/>
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" si="1"/>
+        <v>8.1632653061224438</v>
+      </c>
+      <c r="J9" s="25">
+        <v>1.41</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -3596,25 +4980,35 @@
     </row>
     <row r="10" spans="1:26" ht="18" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="6">
+      <c r="B10" s="24">
         <v>7</v>
       </c>
-      <c r="C10" s="7">
-        <f t="shared" si="1"/>
+      <c r="C10" s="19">
+        <f t="shared" si="2"/>
         <v>0.37000000000000011</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="20">
         <f t="shared" si="0"/>
         <v>7.3046018991964896</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="25">
         <v>0.98380000000000001</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="G10" s="24">
+        <v>7</v>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="3"/>
+        <v>0.37000000000000011</v>
+      </c>
+      <c r="I10" s="20">
+        <f t="shared" si="1"/>
+        <v>7.3046018991964896</v>
+      </c>
+      <c r="J10" s="25">
+        <v>1.26</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -3634,25 +5028,35 @@
     </row>
     <row r="11" spans="1:26" ht="18" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="6">
+      <c r="B11" s="24">
         <v>8</v>
       </c>
-      <c r="C11" s="7">
-        <f t="shared" si="1"/>
+      <c r="C11" s="19">
+        <f t="shared" si="2"/>
         <v>0.39000000000000012</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="20">
         <f t="shared" si="0"/>
         <v>6.5746219592373398</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="25">
         <v>0.90580000000000005</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="G11" s="24">
+        <v>8</v>
+      </c>
+      <c r="H11" s="19">
+        <f t="shared" si="3"/>
+        <v>0.39000000000000012</v>
+      </c>
+      <c r="I11" s="20">
+        <f t="shared" si="1"/>
+        <v>6.5746219592373398</v>
+      </c>
+      <c r="J11" s="25">
+        <v>1.1200000000000001</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3672,25 +5076,35 @@
     </row>
     <row r="12" spans="1:26" ht="18" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="6">
+      <c r="B12" s="24">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
-        <f t="shared" si="1"/>
+      <c r="C12" s="19">
+        <f t="shared" si="2"/>
         <v>0.41000000000000014</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="20">
         <f t="shared" si="0"/>
         <v>5.9488399762046358</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="25">
         <v>0.8337</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="G12" s="24">
+        <v>9</v>
+      </c>
+      <c r="H12" s="19">
+        <f t="shared" si="3"/>
+        <v>0.41000000000000014</v>
+      </c>
+      <c r="I12" s="20">
+        <f t="shared" si="1"/>
+        <v>5.9488399762046358</v>
+      </c>
+      <c r="J12" s="25">
+        <v>1.01</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -3710,25 +5124,35 @@
     </row>
     <row r="13" spans="1:26" ht="18" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="6">
+      <c r="B13" s="24">
         <v>10</v>
       </c>
-      <c r="C13" s="7">
-        <f t="shared" si="1"/>
+      <c r="C13" s="19">
+        <f t="shared" si="2"/>
         <v>0.43000000000000016</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="20">
         <f t="shared" si="0"/>
         <v>5.4083288263926406</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="25">
         <v>0.77980000000000005</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="G13" s="24">
+        <v>10</v>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" si="3"/>
+        <v>0.43000000000000016</v>
+      </c>
+      <c r="I13" s="20">
+        <f t="shared" si="1"/>
+        <v>5.4083288263926406</v>
+      </c>
+      <c r="J13" s="25">
+        <v>0.93</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -3748,25 +5172,35 @@
     </row>
     <row r="14" spans="1:26" ht="18" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="6">
+      <c r="B14" s="24">
         <v>11</v>
       </c>
-      <c r="C14" s="7">
-        <f t="shared" si="1"/>
+      <c r="C14" s="19">
+        <f t="shared" si="2"/>
         <v>0.45000000000000018</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="20">
         <f t="shared" si="0"/>
         <v>4.9382716049382678</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="25">
         <v>0.72</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+      <c r="G14" s="24">
+        <v>11</v>
+      </c>
+      <c r="H14" s="19">
+        <f t="shared" si="3"/>
+        <v>0.45000000000000018</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" si="1"/>
+        <v>4.9382716049382678</v>
+      </c>
+      <c r="J14" s="25">
+        <v>0.86</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -3786,25 +5220,35 @@
     </row>
     <row r="15" spans="1:26" ht="18" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="6">
+      <c r="B15" s="24">
         <v>12</v>
       </c>
-      <c r="C15" s="7">
-        <f t="shared" si="1"/>
+      <c r="C15" s="19">
+        <f t="shared" si="2"/>
         <v>0.4700000000000002</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="20">
         <f t="shared" si="0"/>
         <v>4.5269352648257097</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="25">
         <v>0.66739999999999999</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="G15" s="24">
+        <v>12</v>
+      </c>
+      <c r="H15" s="19">
+        <f t="shared" si="3"/>
+        <v>0.4700000000000002</v>
+      </c>
+      <c r="I15" s="20">
+        <f t="shared" si="1"/>
+        <v>4.5269352648257097</v>
+      </c>
+      <c r="J15" s="25">
+        <v>0.79</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -3824,25 +5268,35 @@
     </row>
     <row r="16" spans="1:26" ht="18" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="6">
+      <c r="B16" s="24">
         <v>13</v>
       </c>
-      <c r="C16" s="7">
-        <f t="shared" si="1"/>
+      <c r="C16" s="19">
+        <f t="shared" si="2"/>
         <v>0.49000000000000021</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="20">
         <f t="shared" si="0"/>
         <v>4.1649312786338992</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="25">
         <v>0.62580000000000002</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+      <c r="G16" s="24">
+        <v>13</v>
+      </c>
+      <c r="H16" s="19">
+        <f t="shared" si="3"/>
+        <v>0.49000000000000021</v>
+      </c>
+      <c r="I16" s="20">
+        <f t="shared" si="1"/>
+        <v>4.1649312786338992</v>
+      </c>
+      <c r="J16" s="25">
+        <v>0.73</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -3862,25 +5316,35 @@
     </row>
     <row r="17" spans="1:26" ht="18" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="10">
+      <c r="B17" s="24">
         <v>14</v>
       </c>
-      <c r="C17" s="11">
-        <f t="shared" si="1"/>
+      <c r="C17" s="19">
+        <f t="shared" si="2"/>
         <v>0.51000000000000023</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="20">
         <f t="shared" si="0"/>
         <v>3.8446751249519382</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="25">
         <v>0.57669999999999999</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+      <c r="G17" s="24">
+        <v>14</v>
+      </c>
+      <c r="H17" s="19">
+        <f t="shared" si="3"/>
+        <v>0.51000000000000023</v>
+      </c>
+      <c r="I17" s="20">
+        <f t="shared" si="1"/>
+        <v>3.8446751249519382</v>
+      </c>
+      <c r="J17" s="25">
+        <v>0.69</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3900,15 +5364,35 @@
     </row>
     <row r="18" spans="1:26" ht="18" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="B18" s="24">
+        <v>15</v>
+      </c>
+      <c r="C18" s="19">
+        <f t="shared" si="2"/>
+        <v>0.53000000000000025</v>
+      </c>
+      <c r="D18" s="20">
+        <f t="shared" si="0"/>
+        <v>3.5599857600569567</v>
+      </c>
+      <c r="E18" s="25">
+        <v>0.54200000000000004</v>
+      </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="G18" s="24">
+        <v>15</v>
+      </c>
+      <c r="H18" s="19">
+        <f t="shared" si="3"/>
+        <v>0.53000000000000025</v>
+      </c>
+      <c r="I18" s="20">
+        <f t="shared" si="1"/>
+        <v>3.5599857600569567</v>
+      </c>
+      <c r="J18" s="25">
+        <v>0.63</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3928,15 +5412,35 @@
     </row>
     <row r="19" spans="1:26" ht="18" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="B19" s="24">
+        <v>16</v>
+      </c>
+      <c r="C19" s="19">
+        <f t="shared" si="2"/>
+        <v>0.55000000000000027</v>
+      </c>
+      <c r="D19" s="20">
+        <f t="shared" si="0"/>
+        <v>3.3057851239669391</v>
+      </c>
+      <c r="E19" s="25">
+        <v>0.49890000000000001</v>
+      </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="G19" s="24">
+        <v>16</v>
+      </c>
+      <c r="H19" s="19">
+        <f t="shared" si="3"/>
+        <v>0.55000000000000027</v>
+      </c>
+      <c r="I19" s="20">
+        <f t="shared" si="1"/>
+        <v>3.3057851239669391</v>
+      </c>
+      <c r="J19" s="25">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -3956,10 +5460,34 @@
     </row>
     <row r="20" spans="1:26" ht="18" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="B20" s="24">
+        <v>17</v>
+      </c>
+      <c r="C20" s="19">
+        <f t="shared" si="2"/>
+        <v>0.57000000000000028</v>
+      </c>
+      <c r="D20" s="20">
+        <f t="shared" si="0"/>
+        <v>3.0778701138811915</v>
+      </c>
+      <c r="E20" s="25">
+        <v>0.46879999999999999</v>
+      </c>
+      <c r="G20" s="24">
+        <v>17</v>
+      </c>
+      <c r="H20" s="19">
+        <f t="shared" si="3"/>
+        <v>0.57000000000000028</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="1"/>
+        <v>3.0778701138811915</v>
+      </c>
+      <c r="J20" s="25">
+        <v>0.51</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3979,10 +5507,34 @@
     </row>
     <row r="21" spans="1:26" ht="29.4" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+      <c r="B21" s="24">
+        <v>18</v>
+      </c>
+      <c r="C21" s="19">
+        <f t="shared" si="2"/>
+        <v>0.5900000000000003</v>
+      </c>
+      <c r="D21" s="20">
+        <f t="shared" si="0"/>
+        <v>2.8727377190462482</v>
+      </c>
+      <c r="E21" s="25">
+        <v>0.4325</v>
+      </c>
+      <c r="G21" s="24">
+        <v>18</v>
+      </c>
+      <c r="H21" s="19">
+        <f t="shared" si="3"/>
+        <v>0.5900000000000003</v>
+      </c>
+      <c r="I21" s="20">
+        <f t="shared" si="1"/>
+        <v>2.8727377190462482</v>
+      </c>
+      <c r="J21" s="25">
+        <v>0.49</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -4000,12 +5552,36 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="27" customHeight="1">
+    <row r="22" spans="1:26" ht="27" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+      <c r="B22" s="26">
+        <v>19</v>
+      </c>
+      <c r="C22" s="27">
+        <f t="shared" si="2"/>
+        <v>0.61000000000000032</v>
+      </c>
+      <c r="D22" s="28">
+        <f t="shared" si="0"/>
+        <v>2.687449610319804</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0.41489999999999999</v>
+      </c>
+      <c r="G22" s="26">
+        <v>19</v>
+      </c>
+      <c r="H22" s="27">
+        <f t="shared" si="3"/>
+        <v>0.61000000000000032</v>
+      </c>
+      <c r="I22" s="28">
+        <f t="shared" si="1"/>
+        <v>2.687449610319804</v>
+      </c>
+      <c r="J22" s="29">
+        <v>0.43</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -4056,7 +5632,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="14"/>
+      <c r="O24" s="7"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -4324,13 +5900,13 @@
     </row>
     <row r="36" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -4352,21 +5928,21 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="18" customHeight="1" thickTop="1">
+    <row r="37" spans="1:26" ht="18" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="42" t="s">
+      <c r="E37" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F37" s="16"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -4390,11 +5966,11 @@
     </row>
     <row r="38" spans="1:26" ht="18" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="9"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -4418,20 +5994,20 @@
     </row>
     <row r="39" spans="1:26" ht="18" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="10">
         <f>8.22*10^14</f>
         <v>822000000000000.13</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="11">
         <v>7.3599999999999999E-2</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="47">
         <v>1.3540000000000001</v>
       </c>
-      <c r="F39" s="16"/>
+      <c r="F39" s="9"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -4455,20 +6031,20 @@
     </row>
     <row r="40" spans="1:26" ht="18" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="10">
         <f>7.41*10^14</f>
         <v>741000000000000</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="11">
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="47">
         <v>1.2070000000000001</v>
       </c>
-      <c r="F40" s="16"/>
+      <c r="F40" s="9"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -4492,20 +6068,20 @@
     </row>
     <row r="41" spans="1:26" ht="18" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="10">
         <f>6.88*10^14</f>
         <v>688000000000000</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="11">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="47">
         <v>1.036</v>
       </c>
-      <c r="F41" s="16"/>
+      <c r="F41" s="9"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -4529,20 +6105,20 @@
     </row>
     <row r="42" spans="1:26" ht="18" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="10">
         <f>5.49*10^14</f>
         <v>549000000000000</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="11">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="47">
         <v>0.629</v>
       </c>
-      <c r="F42" s="16"/>
+      <c r="F42" s="9"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -4566,20 +6142,20 @@
     </row>
     <row r="43" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C43" s="49">
         <f>5.2*10^14</f>
         <v>520000000000000</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="50">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="51">
         <v>0.4047</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="1"/>
@@ -4603,18 +6179,18 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="18" customHeight="1" thickTop="1">
+    <row r="44" spans="1:26" ht="18" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="36">
+      <c r="C44" s="31"/>
+      <c r="D44" s="32">
         <f>3*10^-15</f>
         <v>3.0000000000000002E-15</v>
       </c>
       <c r="E44" s="33"/>
-      <c r="F44" s="25">
+      <c r="F44" s="12">
         <f>D45/1.6/10^-19</f>
         <v>4.1437500000000003E-15</v>
       </c>
@@ -4641,16 +6217,16 @@
     </row>
     <row r="45" spans="1:26" ht="18" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="36">
+      <c r="C45" s="17"/>
+      <c r="D45" s="15">
         <f>6.63*10^-34</f>
         <v>6.6300000000000008E-34</v>
       </c>
-      <c r="E45" s="37"/>
-      <c r="F45" s="16"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="9"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -4674,16 +6250,16 @@
     </row>
     <row r="46" spans="1:26" ht="18" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="32">
+      <c r="C46" s="17"/>
+      <c r="D46" s="18">
         <f>D44* 1.6 * 10^-19</f>
         <v>4.8000000000000007E-34</v>
       </c>
-      <c r="E46" s="33"/>
-      <c r="F46" s="16"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="9"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -4707,16 +6283,16 @@
     </row>
     <row r="47" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="34">
+      <c r="C47" s="38"/>
+      <c r="D47" s="39">
         <f>ABS((D45-D46)/D45)</f>
         <v>0.27601809954751128</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="16"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="9"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -4738,7 +6314,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="18" customHeight="1" thickTop="1" thickBot="1">
+    <row r="48" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -4771,7 +6347,7 @@
       <c r="B49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="1"/>
@@ -4800,10 +6376,10 @@
     </row>
     <row r="50" spans="1:26" ht="18" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="13">
         <f>(D44*C39-1.6*10^-19*E39)/1.6/10^-19</f>
         <v>1.5412500000000002E+19</v>
       </c>
@@ -4833,10 +6409,10 @@
     </row>
     <row r="51" spans="1:26" ht="18" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="26">
+      <c r="C51" s="13">
         <f>(D44*C40-1.6*10^-19*E40)/1.6/10^-19</f>
         <v>1.389375E+19</v>
       </c>
@@ -4866,10 +6442,10 @@
     </row>
     <row r="52" spans="1:26" ht="18" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="13">
         <f>(D44*C41-1.6*10^-19*E41)/1.6/10^-19</f>
         <v>1.29E+19</v>
       </c>
@@ -4899,10 +6475,10 @@
     </row>
     <row r="53" spans="1:26" ht="18" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="26">
+      <c r="C53" s="13">
         <f>(D44*C42-1.6*10^-19*E42)/1.6/10^-19</f>
         <v>1.029375E+19</v>
       </c>
@@ -4932,10 +6508,10 @@
     </row>
     <row r="54" spans="1:26" ht="18" customHeight="1" thickBot="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="14">
         <f>(D44*C43-1.6*10^-19*E43)/1.6/10^-19</f>
         <v>9.75E+18</v>
       </c>
@@ -31453,6 +33029,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="B37:B38"/>
@@ -31461,10 +33041,6 @@
     <mergeCell ref="E37:E38"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
